--- a/data/trans_dic/P16A_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P16A_R-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido algún psicofármaco en las dos últimas semanas</t>
+          <t>Población que ha consumido algún psicofármaco en las dos últimas semanas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,51</t>
+          <t>0,18; 1,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,86</t>
+          <t>0,58; 2,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,57</t>
+          <t>0,25; 2,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,11; 5,87</t>
+          <t>0,08; 6,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,2; 5,54</t>
+          <t>2,13; 5,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,56; 5,07</t>
+          <t>1,62; 5,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,62; 5,11</t>
+          <t>1,61; 5,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,0; 8,9</t>
+          <t>1,92; 8,9</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,31; 3,18</t>
+          <t>1,36; 3,1</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,28; 3,21</t>
+          <t>1,22; 3,19</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,21</t>
+          <t>1,2; 3,19</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,27; 5,13</t>
+          <t>1,31; 5,36</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,78; 4,3</t>
+          <t>1,79; 4,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,43; 5,7</t>
+          <t>2,56; 6,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,87</t>
+          <t>1,34; 3,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,84; 4,59</t>
+          <t>0,78; 4,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,01; 6,6</t>
+          <t>2,97; 6,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,73; 7,85</t>
+          <t>3,72; 7,64</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,34; 5,35</t>
+          <t>2,17; 5,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,19; 6,45</t>
+          <t>2,21; 6,4</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,69; 4,73</t>
+          <t>2,61; 4,62</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,52; 6,03</t>
+          <t>3,51; 6,12</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,1; 4,09</t>
+          <t>2,15; 4,07</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,92; 4,69</t>
+          <t>1,98; 4,63</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,72; 4,33</t>
+          <t>1,77; 4,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,95; 8,06</t>
+          <t>4,0; 8,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,52; 7,11</t>
+          <t>3,7; 7,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,88; 8,11</t>
+          <t>3,91; 7,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,0; 10,21</t>
+          <t>6,06; 10,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,55; 14,28</t>
+          <t>9,64; 14,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,02; 11,19</t>
+          <t>7,17; 11,72</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,58; 11,14</t>
+          <t>6,28; 11,06</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,29; 6,83</t>
+          <t>4,21; 6,77</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,44; 10,68</t>
+          <t>7,4; 10,56</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,66; 8,55</t>
+          <t>5,83; 8,54</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,86; 9,05</t>
+          <t>6,02; 8,97</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,68; 7,8</t>
+          <t>3,62; 7,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,73; 9,08</t>
+          <t>4,9; 9,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,99; 9,35</t>
+          <t>5,16; 9,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,88; 10,41</t>
+          <t>2,92; 10,46</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,87; 16,67</t>
+          <t>10,65; 16,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,88; 19,91</t>
+          <t>13,86; 20,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,33; 18,53</t>
+          <t>12,57; 18,3</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,1; 17,74</t>
+          <t>11,98; 17,49</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,82; 11,66</t>
+          <t>7,62; 11,41</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,77; 13,68</t>
+          <t>9,94; 13,86</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,35; 13,02</t>
+          <t>9,44; 13,17</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,28; 12,92</t>
+          <t>6,31; 12,94</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,46; 10,92</t>
+          <t>5,34; 10,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,97; 13,9</t>
+          <t>7,85; 13,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,31; 12,11</t>
+          <t>6,49; 12,12</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,64; 14,9</t>
+          <t>9,76; 14,66</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,91; 22,78</t>
+          <t>14,83; 22,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,55; 27,58</t>
+          <t>19,52; 27,09</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,56; 30,96</t>
+          <t>22,31; 30,24</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>22,46; 27,83</t>
+          <t>22,46; 28,21</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11,09; 15,79</t>
+          <t>11,21; 15,92</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14,68; 20,15</t>
+          <t>14,81; 19,71</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15,2; 20,18</t>
+          <t>15,33; 20,54</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,55; 20,29</t>
+          <t>16,57; 20,41</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,96; 13,81</t>
+          <t>6,93; 13,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7,26; 15,26</t>
+          <t>7,39; 15,66</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,46; 13,86</t>
+          <t>7,56; 13,71</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9,78; 15,0</t>
+          <t>9,37; 14,89</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>16,39; 24,45</t>
+          <t>16,1; 24,22</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21,14; 30,31</t>
+          <t>21,17; 31,01</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>25,27; 34,93</t>
+          <t>24,85; 34,74</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,79; 29,05</t>
+          <t>7,95; 29,08</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12,96; 18,26</t>
+          <t>13,05; 18,33</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>15,52; 22,09</t>
+          <t>15,84; 21,81</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>17,73; 23,92</t>
+          <t>17,86; 23,9</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8,94; 21,42</t>
+          <t>8,17; 21,4</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>10,67; 20,21</t>
+          <t>10,76; 20,41</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,8; 19,65</t>
+          <t>10,12; 19,94</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10,88; 18,85</t>
+          <t>11,41; 19,29</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19,48; 26,98</t>
+          <t>19,07; 26,97</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>14,42; 23,29</t>
+          <t>14,75; 23,36</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,6; 37,64</t>
+          <t>27,24; 37,43</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,11; 31,01</t>
+          <t>20,99; 31,37</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>33,75; 40,34</t>
+          <t>34,09; 40,58</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>14,19; 21,12</t>
+          <t>14,4; 21,09</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21,41; 28,94</t>
+          <t>21,8; 29,01</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18,45; 25,18</t>
+          <t>18,19; 24,91</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>29,2; 34,17</t>
+          <t>28,98; 34,07</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,21; 5,75</t>
+          <t>4,2; 5,7</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,81; 7,62</t>
+          <t>5,79; 7,65</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,51; 7,16</t>
+          <t>5,44; 7,09</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6,53; 9,39</t>
+          <t>6,43; 9,27</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>10,1; 12,25</t>
+          <t>10,06; 12,09</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,42; 16,8</t>
+          <t>14,27; 16,75</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,98; 16,45</t>
+          <t>13,94; 16,47</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>12,89; 17,68</t>
+          <t>13,22; 17,8</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7,45; 8,85</t>
+          <t>7,51; 8,75</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10,43; 12,04</t>
+          <t>10,48; 12,04</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10,04; 11,57</t>
+          <t>10,08; 11,54</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>10,81; 13,44</t>
+          <t>10,6; 13,41</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido algún psicofármaco en las dos últimas semanas</t>
+          <t>Población que ha consumido algún psicofármaco en las dos últimas semanas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>908; 7456</t>
+          <t>912; 7696</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2649; 12972</t>
+          <t>2644; 12803</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1060; 10790</t>
+          <t>1057; 10293</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>450; 23460</t>
+          <t>317; 25637</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>10262; 25903</t>
+          <t>9945; 26022</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6725; 21797</t>
+          <t>6960; 21560</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6393; 20239</t>
+          <t>6365; 20506</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6273; 27871</t>
+          <t>6003; 27887</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12637; 30622</t>
+          <t>13092; 29780</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11311; 28370</t>
+          <t>10773; 28213</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9527; 26159</t>
+          <t>9818; 26041</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9049; 36566</t>
+          <t>9347; 38229</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13114; 31611</t>
+          <t>13166; 31165</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16674; 39152</t>
+          <t>17576; 41860</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7979; 22835</t>
+          <t>7886; 22721</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3566; 19444</t>
+          <t>3312; 17413</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18837; 41277</t>
+          <t>18568; 40041</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22758; 47902</t>
+          <t>22685; 46623</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13203; 30164</t>
+          <t>12254; 29708</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11232; 33044</t>
+          <t>11316; 32782</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>36587; 64432</t>
+          <t>35456; 62941</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>45718; 78292</t>
+          <t>45599; 79457</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>24192; 47236</t>
+          <t>24824; 46994</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17989; 43850</t>
+          <t>18524; 43298</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10956; 27679</t>
+          <t>11310; 28248</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>26933; 54943</t>
+          <t>27263; 55631</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23521; 47593</t>
+          <t>24744; 48703</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20829; 43500</t>
+          <t>20953; 42743</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>41408; 70422</t>
+          <t>41780; 70216</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>67892; 101480</t>
+          <t>68530; 102482</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>46397; 74002</t>
+          <t>47407; 77496</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>38934; 65957</t>
+          <t>37186; 65455</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>56938; 90735</t>
+          <t>55883; 89883</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>103552; 148779</t>
+          <t>103111; 147121</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>75332; 113799</t>
+          <t>77621; 113598</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>66169; 102065</t>
+          <t>67946; 101266</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>19091; 40491</t>
+          <t>18803; 40429</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>29045; 55798</t>
+          <t>30097; 56564</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>32254; 60377</t>
+          <t>33345; 58618</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>25531; 92411</t>
+          <t>25956; 92820</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>56054; 85946</t>
+          <t>54934; 85495</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>85515; 122654</t>
+          <t>85417; 123850</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>80056; 120290</t>
+          <t>81584; 118778</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>86256; 126496</t>
+          <t>85410; 124707</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>80932; 120681</t>
+          <t>78838; 118098</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>120228; 168332</t>
+          <t>122291; 170650</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>121150; 168673</t>
+          <t>122244; 170622</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>100454; 206851</t>
+          <t>100968; 207135</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>21129; 42242</t>
+          <t>20633; 41450</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>34208; 59709</t>
+          <t>33691; 59953</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>30167; 57857</t>
+          <t>31033; 57937</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>54125; 83606</t>
+          <t>54792; 82292</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>60235; 92031</t>
+          <t>59922; 92769</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>87551; 123511</t>
+          <t>87393; 121300</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>112071; 153830</t>
+          <t>110834; 150226</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>123057; 152502</t>
+          <t>123048; 154551</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>87675; 124888</t>
+          <t>88676; 125868</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>128812; 176757</t>
+          <t>129941; 172898</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>148175; 196754</t>
+          <t>149417; 200245</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>183530; 225035</t>
+          <t>183783; 226382</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>20374; 40396</t>
+          <t>20278; 39283</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>22482; 47265</t>
+          <t>22884; 48525</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>24941; 46328</t>
+          <t>25286; 45822</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>36020; 55242</t>
+          <t>34483; 54831</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>56205; 83852</t>
+          <t>55215; 83053</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>74836; 107302</t>
+          <t>74943; 109759</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>95470; 131940</t>
+          <t>93890; 131249</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>47397; 176734</t>
+          <t>48393; 176921</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>82332; 116039</t>
+          <t>82964; 116487</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>102990; 146659</t>
+          <t>105110; 144740</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>126243; 170307</t>
+          <t>127151; 170184</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>87263; 209206</t>
+          <t>79752; 208967</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>22386; 42425</t>
+          <t>22592; 42837</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>24478; 49094</t>
+          <t>25286; 49813</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>27974; 48448</t>
+          <t>29324; 49578</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>55079; 76284</t>
+          <t>53923; 76265</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>48150; 77758</t>
+          <t>49235; 78009</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>107340; 146417</t>
+          <t>105976; 145607</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>84492; 124081</t>
+          <t>83996; 125550</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>143709; 171762</t>
+          <t>145164; 172816</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>77152; 114863</t>
+          <t>78300; 114659</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>136791; 184907</t>
+          <t>139285; 185322</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>121243; 165465</t>
+          <t>119541; 163695</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>206899; 242133</t>
+          <t>205332; 241399</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>137978; 188322</t>
+          <t>137711; 186644</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>198997; 261076</t>
+          <t>198349; 262165</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>187163; 243107</t>
+          <t>184534; 240749</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>225782; 324905</t>
+          <t>222400; 320799</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>341295; 413853</t>
+          <t>339971; 408540</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>513093; 597912</t>
+          <t>507726; 595880</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>495516; 583035</t>
+          <t>494082; 583729</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>478497; 656282</t>
+          <t>490632; 660644</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>495709; 588787</t>
+          <t>499543; 582131</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>728374; 840686</t>
+          <t>732170; 840872</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>696759; 802928</t>
+          <t>699388; 800588</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>775592; 964118</t>
+          <t>760517; 961645</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P16A_R-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,56</t>
+          <t>0,18; 1,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,82</t>
+          <t>0,61; 2,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,45</t>
+          <t>0,25; 2,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,08; 6,41</t>
+          <t>0,31; 4,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,13; 5,57</t>
+          <t>2,23; 5,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,62; 5,01</t>
+          <t>1,39; 4,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,61; 5,18</t>
+          <t>1,66; 5,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,92; 8,9</t>
+          <t>1,75; 8,56</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,36; 3,1</t>
+          <t>1,36; 3,17</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,22; 3,19</t>
+          <t>1,33; 3,23</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,2; 3,19</t>
+          <t>1,17; 3,18</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,31; 5,36</t>
+          <t>1,37; 4,97</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,79; 4,24</t>
+          <t>1,85; 4,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,56; 6,09</t>
+          <t>2,4; 5,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,34; 3,85</t>
+          <t>1,33; 3,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,78; 4,11</t>
+          <t>1,09; 4,35</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,97; 6,4</t>
+          <t>2,98; 6,47</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,72; 7,64</t>
+          <t>3,91; 7,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,17; 5,27</t>
+          <t>2,3; 5,21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,21; 6,4</t>
+          <t>2,65; 6,47</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,61; 4,62</t>
+          <t>2,71; 4,76</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,51; 6,12</t>
+          <t>3,49; 6,0</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,15; 4,07</t>
+          <t>2,08; 3,95</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,98; 4,63</t>
+          <t>2,25; 4,72</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,77; 4,42</t>
+          <t>1,77; 4,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,0; 8,16</t>
+          <t>3,92; 7,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,7; 7,28</t>
+          <t>3,69; 7,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,91; 7,97</t>
+          <t>3,4; 7,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,06; 10,18</t>
+          <t>5,87; 10,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,64; 14,42</t>
+          <t>9,59; 14,41</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,17; 11,72</t>
+          <t>7,11; 11,33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,28; 11,06</t>
+          <t>7,54; 11,36</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,21; 6,77</t>
+          <t>4,26; 6,73</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,4; 10,56</t>
+          <t>7,25; 10,42</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,83; 8,54</t>
+          <t>5,72; 8,55</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,02; 8,97</t>
+          <t>5,91; 8,68</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>12,02%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,62; 7,79</t>
+          <t>3,75; 8,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,9; 9,2</t>
+          <t>4,89; 9,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,16; 9,07</t>
+          <t>5,09; 9,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,92; 10,46</t>
+          <t>7,29; 11,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,65; 16,58</t>
+          <t>10,93; 16,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,86; 20,1</t>
+          <t>13,83; 20,16</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,57; 18,3</t>
+          <t>12,52; 18,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,98; 17,49</t>
+          <t>12,57; 16,69</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,62; 11,41</t>
+          <t>7,87; 11,48</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,94; 13,86</t>
+          <t>10,01; 13,72</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,44; 13,17</t>
+          <t>9,34; 12,88</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,31; 12,94</t>
+          <t>10,39; 13,72</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,47%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,34; 10,72</t>
+          <t>5,43; 10,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,85; 13,96</t>
+          <t>7,62; 13,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,49; 12,12</t>
+          <t>6,41; 12,03</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,76; 14,66</t>
+          <t>9,53; 14,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,83; 22,96</t>
+          <t>15,05; 22,8</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,52; 27,09</t>
+          <t>20,03; 27,79</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,31; 30,24</t>
+          <t>22,16; 30,56</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>22,46; 28,21</t>
+          <t>22,37; 28,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11,21; 15,92</t>
+          <t>11,11; 15,7</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14,81; 19,71</t>
+          <t>14,6; 19,79</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15,33; 20,54</t>
+          <t>15,31; 20,54</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,57; 20,41</t>
+          <t>16,62; 20,42</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>20,51%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,93; 13,43</t>
+          <t>7,01; 13,64</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7,39; 15,66</t>
+          <t>7,4; 15,16</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,56; 13,71</t>
+          <t>7,35; 13,92</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9,37; 14,89</t>
+          <t>9,18; 14,4</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>16,1; 24,22</t>
+          <t>16,18; 24,4</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21,17; 31,01</t>
+          <t>21,12; 30,64</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>24,85; 34,74</t>
+          <t>25,28; 35,18</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,95; 29,08</t>
+          <t>25,47; 31,84</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13,05; 18,33</t>
+          <t>12,82; 18,28</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>15,84; 21,81</t>
+          <t>15,73; 22,0</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>17,86; 23,9</t>
+          <t>17,68; 23,83</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8,17; 21,4</t>
+          <t>18,59; 22,74</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>37,19%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,45%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>10,76; 20,41</t>
+          <t>10,57; 20,12</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10,12; 19,94</t>
+          <t>10,04; 19,74</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11,41; 19,29</t>
+          <t>11,15; 19,14</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19,07; 26,97</t>
+          <t>19,05; 27,23</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>14,75; 23,36</t>
+          <t>14,67; 23,82</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,24; 37,43</t>
+          <t>27,44; 37,74</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,99; 31,37</t>
+          <t>21,08; 31,36</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>34,09; 40,58</t>
+          <t>34,15; 40,51</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>14,4; 21,09</t>
+          <t>14,18; 21,08</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21,8; 29,01</t>
+          <t>21,51; 28,75</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18,19; 24,91</t>
+          <t>18,47; 25,33</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>28,98; 34,07</t>
+          <t>29,24; 34,36</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>13,17%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,2; 5,7</t>
+          <t>4,14; 5,72</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,79; 7,65</t>
+          <t>5,7; 7,59</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,44; 7,09</t>
+          <t>5,51; 7,17</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6,43; 9,27</t>
+          <t>7,67; 9,6</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>10,06; 12,09</t>
+          <t>10,14; 12,2</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,27; 16,75</t>
+          <t>14,5; 16,94</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,94; 16,47</t>
+          <t>14,11; 16,54</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>13,22; 17,8</t>
+          <t>16,41; 18,46</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7,51; 8,75</t>
+          <t>7,44; 8,81</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10,48; 12,04</t>
+          <t>10,42; 11,95</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10,08; 11,54</t>
+          <t>10,04; 11,57</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>10,6; 13,41</t>
+          <t>12,46; 13,88</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>6351</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14276</t>
+          <t>15138</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>19602</t>
+          <t>21489</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>912; 7696</t>
+          <t>904; 8378</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2644; 12803</t>
+          <t>2785; 12652</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1057; 10293</t>
+          <t>1056; 11166</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>317; 25637</t>
+          <t>1249; 19474</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9945; 26022</t>
+          <t>10437; 27237</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6960; 21560</t>
+          <t>5967; 21136</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6365; 20506</t>
+          <t>6578; 21049</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6003; 27887</t>
+          <t>6332; 31014</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>13092; 29780</t>
+          <t>13035; 30474</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10773; 28213</t>
+          <t>11719; 28544</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9818; 26041</t>
+          <t>9499; 25914</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9347; 38229</t>
+          <t>10543; 38273</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8433</t>
+          <t>11012</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>21093</t>
+          <t>21488</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>29526</t>
+          <t>32500</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13166; 31165</t>
+          <t>13592; 31283</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17576; 41860</t>
+          <t>16489; 39650</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7886; 22721</t>
+          <t>7869; 21852</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3312; 17413</t>
+          <t>5179; 20739</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18568; 40041</t>
+          <t>18654; 40486</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22685; 46623</t>
+          <t>23858; 48170</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12254; 29708</t>
+          <t>12982; 29371</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11316; 32782</t>
+          <t>13309; 32465</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>35456; 62941</t>
+          <t>36900; 64814</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>45599; 79457</t>
+          <t>45278; 77801</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>24824; 46994</t>
+          <t>24006; 45624</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18524; 43298</t>
+          <t>22013; 46235</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30546</t>
+          <t>31430</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>52485</t>
+          <t>57341</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>83030</t>
+          <t>88771</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>11310; 28248</t>
+          <t>11297; 28028</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>27263; 55631</t>
+          <t>26752; 54329</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24744; 48703</t>
+          <t>24675; 49695</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20953; 42743</t>
+          <t>21113; 45621</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>41780; 70216</t>
+          <t>40469; 69355</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>68530; 102482</t>
+          <t>68202; 102434</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>47407; 77496</t>
+          <t>47037; 74958</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>37186; 65455</t>
+          <t>46962; 70815</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>55883; 89883</t>
+          <t>56574; 89370</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>103111; 147121</t>
+          <t>101032; 145085</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>77621; 113598</t>
+          <t>76146; 113806</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>67946; 101266</t>
+          <t>73578; 107928</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>60521</t>
+          <t>65294</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>105388</t>
+          <t>107483</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>165909</t>
+          <t>172777</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18803; 40429</t>
+          <t>19462; 41623</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>30097; 56564</t>
+          <t>30050; 56258</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>33345; 58618</t>
+          <t>32855; 59330</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>25956; 92820</t>
+          <t>51064; 83384</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>54934; 85495</t>
+          <t>56364; 85606</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>85417; 123850</t>
+          <t>85228; 124256</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>81584; 118778</t>
+          <t>81273; 118822</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>85410; 124707</t>
+          <t>92610; 122952</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>78838; 118098</t>
+          <t>81429; 118754</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>122291; 170650</t>
+          <t>123234; 168862</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>122244; 170622</t>
+          <t>121002; 166843</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>100968; 207135</t>
+          <t>149393; 197204</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>67729</t>
+          <t>72319</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>137397</t>
+          <t>152631</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>205127</t>
+          <t>224950</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>20633; 41450</t>
+          <t>20996; 42021</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>33691; 59953</t>
+          <t>32714; 58268</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>31033; 57937</t>
+          <t>30616; 57508</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>54792; 82292</t>
+          <t>58044; 88206</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>59922; 92769</t>
+          <t>60785; 92126</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>87393; 121300</t>
+          <t>89708; 124428</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>110834; 150226</t>
+          <t>110078; 151820</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>123048; 154551</t>
+          <t>136197; 170478</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>88676; 125868</t>
+          <t>87834; 124145</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>129941; 172898</t>
+          <t>128055; 173647</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>149417; 200245</t>
+          <t>149229; 200195</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>183783; 226382</t>
+          <t>202452; 248700</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>45109</t>
+          <t>48273</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>113038</t>
+          <t>125319</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>158148</t>
+          <t>173592</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>20278; 39283</t>
+          <t>20500; 39913</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>22884; 48525</t>
+          <t>22913; 46977</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>25286; 45822</t>
+          <t>24561; 46547</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>34483; 54831</t>
+          <t>37356; 58624</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>55215; 83053</t>
+          <t>55475; 83663</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>74943; 109759</t>
+          <t>74755; 108454</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>93890; 131249</t>
+          <t>95484; 132908</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>48393; 176921</t>
+          <t>111867; 139822</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>82964; 116487</t>
+          <t>81458; 116181</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>105110; 144740</t>
+          <t>104383; 146021</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>127151; 170184</t>
+          <t>125918; 169691</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>79752; 208967</t>
+          <t>157318; 192424</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>64938</t>
+          <t>70631</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>158365</t>
+          <t>173072</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>223303</t>
+          <t>243704</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>22592; 42837</t>
+          <t>22195; 42223</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>25286; 49813</t>
+          <t>25097; 49317</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>29324; 49578</t>
+          <t>28650; 49181</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>53923; 76265</t>
+          <t>59079; 84455</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>49235; 78009</t>
+          <t>48994; 79547</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>105976; 145607</t>
+          <t>106733; 146818</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>83996; 125550</t>
+          <t>84350; 125482</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>145164; 172816</t>
+          <t>158645; 188235</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>78300; 114659</t>
+          <t>77113; 114635</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>139285; 185322</t>
+          <t>137403; 183668</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>119541; 163695</t>
+          <t>121353; 166430</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>205332; 241399</t>
+          <t>226569; 266215</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>282602</t>
+          <t>305311</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>602042</t>
+          <t>652472</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>884644</t>
+          <t>957783</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>137711; 186644</t>
+          <t>135663; 187471</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>198349; 262165</t>
+          <t>195270; 259956</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>184534; 240749</t>
+          <t>186862; 243370</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>222400; 320799</t>
+          <t>270968; 339187</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>339971; 408540</t>
+          <t>342761; 412231</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>507726; 595880</t>
+          <t>515873; 602809</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>494082; 583729</t>
+          <t>500061; 586337</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>490632; 660644</t>
+          <t>613414; 689803</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>499543; 582131</t>
+          <t>495382; 586238</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>732170; 840872</t>
+          <t>727951; 834702</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>699388; 800588</t>
+          <t>696469; 802855</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>760517; 961645</t>
+          <t>906063; 1009350</t>
         </is>
       </c>
     </row>
